--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB388E0-FE7C-4D0C-88C7-B3643147DBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F57E26-D65A-41C0-9091-A7666E9B3846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="1755" windowWidth="21600" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOns" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Description</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>2 TB add on</t>
+  </si>
+  <si>
+    <t>10 TB add on</t>
   </si>
 </sst>
 </file>
@@ -155,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -169,6 +172,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,26 +500,26 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7">
+        <v>10000</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46218</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B3" s="7">
         <v>5000</v>
       </c>
-      <c r="C2" s="4">
-        <v>46247</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>5000</v>
-      </c>
-      <c r="C3" s="4">
-        <v>46259</v>
+      <c r="C3" s="8">
+        <v>46225</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -526,44 +531,50 @@
         <v>5000</v>
       </c>
       <c r="C4" s="4">
-        <v>46261</v>
+        <v>46247</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46259</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46261</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B7" s="3">
         <v>2000</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C7" s="4">
         <v>46262</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -820,10 +831,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid GB" error="Enter the add-on size in GB, e.g. 5000 for a 5 TB package." sqref="B2:B39" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid GB" error="Enter the add-on size in GB, e.g. 5000 for a 5 TB package." sqref="B10:B39 B4:B7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter the purchase date, e.g. 2026-08-22." sqref="C2:C39" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter the purchase date, e.g. 2026-08-22." sqref="C10:C39 C4:C7" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>

--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F57E26-D65A-41C0-9091-A7666E9B3846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C938AC96-5826-48D1-AAED-9BD6629A902C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Description</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>10 TB add on</t>
+  </si>
+  <si>
+    <t>20 TB add on</t>
   </si>
 </sst>
 </file>
@@ -158,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -174,6 +177,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,6 +576,15 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46286</v>
+      </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">

--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C938AC96-5826-48D1-AAED-9BD6629A902C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9272E297-9CDD-436F-8FB1-CD0F2763F045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
         <v>20000</v>
       </c>
       <c r="C8" s="8">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="D8" s="2"/>
     </row>

--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9272E297-9CDD-436F-8FB1-CD0F2763F045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E238169-19F6-464A-9958-0B513CE1A070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Description</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>20 TB add on</t>
+  </si>
+  <si>
+    <t>12 TB add on</t>
   </si>
 </sst>
 </file>
@@ -588,6 +591,15 @@
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="7">
+        <v>12000</v>
+      </c>
+      <c r="C9" s="8">
+        <v>46289</v>
+      </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
